--- a/docs/table/核价测试数据/核价系统功能基础数据功能结构所需字段（6.0版） .xlsx
+++ b/docs/table/核价测试数据/核价系统功能基础数据功能结构所需字段（6.0版） .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\核价测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3114F7-5AED-491B-B941-96FDED20A06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5CFB18-9ABF-4DE0-A981-78CD35F393A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素核价价格表" sheetId="11" r:id="rId1"/>
@@ -60,11 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="285">
-  <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="280">
   <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -333,10 +329,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>电镀方案编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -644,10 +636,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -684,10 +672,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>非生产能耗单价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -708,10 +692,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -752,10 +732,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -780,10 +756,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -860,10 +832,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宏丰料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>工序编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -940,14 +908,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.按元素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.按材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>密度（g/cm3)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -991,10 +951,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>物料料号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>材料损耗率（%）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1147,6 +1103,28 @@
   </si>
   <si>
     <t>8DLX.550.666</t>
+  </si>
+  <si>
+    <t>生产料号</t>
+  </si>
+  <si>
+    <t>销售料号</t>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材质料号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售料号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1302,7 +1280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1368,6 +1346,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1666,39 +1647,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1">
         <v>5800</v>
@@ -1707,19 +1688,19 @@
         <v>5850.5</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I2" s="1">
         <v>85</v>
@@ -1730,7 +1711,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1">
         <v>65</v>
@@ -1739,19 +1720,19 @@
         <v>66.2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I3" s="1">
         <v>40</v>
@@ -1762,7 +1743,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1">
         <v>180</v>
@@ -1771,19 +1752,19 @@
         <v>182.5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I4" s="1">
         <v>25</v>
@@ -1803,168 +1784,206 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="1">
+        <v>154</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="L2" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>1E-3</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J3" s="1">
+        <v>145</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="L3" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.04</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4" s="1">
+        <v>145</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+      <c r="L4" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="1">
+        <v>111</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1">
         <v>1.4000000000000001E-7</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J5" s="1">
+        <v>145</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="L5" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1978,168 +1997,206 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>159</v>
+        <v>274</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+        <v>39</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.01</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="L2" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.03</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="1">
+        <v>141</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="L3" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.05</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J4" s="1">
+        <v>141</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+      <c r="L4" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="1">
+        <v>111</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J5" s="1">
+        <v>154</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="L5" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2152,150 +2209,192 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="H1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="M1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+      <c r="P1" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>8204180004</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>300</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>10000</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>2</v>
       </c>
-      <c r="L2" s="1">
-        <f>I2/J2/K2</f>
+      <c r="M2" s="1">
+        <f>J2/K2/L2</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+        <v>117</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" s="1">
+        <v>103</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>8204180007</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>320</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>12000</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>2</v>
       </c>
-      <c r="L3" s="1">
-        <f>I3/J3/K3</f>
+      <c r="M3" s="1">
+        <f>J3/K3/L3</f>
         <v>1.3333333333333334E-2</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2309,142 +2408,182 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="11.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.125" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="21.125" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.01</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J2" s="1">
+        <v>168</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K2" s="1">
         <v>2001</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="L2" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.03</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="1">
+        <v>168</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="1">
         <v>2001</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="L3" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.05</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4" s="1">
+        <v>145</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="1">
         <v>2001</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="L4" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2458,84 +2597,128 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+        <v>118</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" s="1">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J2" s="1">
+        <v>85</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="1">
         <v>2001</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="L2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2548,98 +2731,140 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.875" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.875" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+      <c r="K1" s="19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="21">
+      <c r="D2" s="21">
         <v>2120011658</v>
       </c>
-      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
         <v>5.5</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="18">
+        <v>124</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K2" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="21">
+      <c r="D3" s="21">
         <v>2120011659</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="18">
+        <v>85</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="18">
         <v>2</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2653,100 +2878,142 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="I1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
+        <v>3120018220</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21">
+      <c r="D2" s="21">
         <v>2120011658</v>
       </c>
-      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
         <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="21">
+      <c r="D3" s="21">
         <v>2120011659</v>
       </c>
-      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
         <v>2</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.5</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2760,81 +3027,125 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="I1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
+        <v>3120018220</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21">
+      <c r="D2" s="21">
         <v>2120011658</v>
       </c>
-      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="I2" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J2" s="1">
         <v>1.2</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2848,153 +3159,191 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>1.2</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" s="1">
+        <v>124</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>2.1</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J3" s="1">
+        <v>131</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>2</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="1">
+        <v>131</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="1">
+        <v>111</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1">
         <v>0.5</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J5" s="1">
+        <v>187</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K5" s="1">
         <v>0</v>
       </c>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3005,83 +3354,125 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>196</v>
+        <v>135</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+        <v>191</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
         <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.5</v>
       </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3110,43 +3501,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L1" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -3154,13 +3545,13 @@
         <v>1610010128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1">
         <v>55</v>
@@ -3169,19 +3560,19 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L2" s="1">
         <v>40</v>
@@ -3195,13 +3586,13 @@
         <v>1220030090</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="E3" s="1">
         <v>68</v>
@@ -3210,19 +3601,19 @@
         <v>69.2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="L3" s="1">
         <v>40</v>
@@ -3239,93 +3630,135 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" customWidth="1"/>
-    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+        <v>219</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.8</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+        <v>85</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.2</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3350,33 +3783,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" s="14" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1">
         <v>2000</v>
@@ -3385,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1">
         <v>3.1E-2</v>
@@ -3394,7 +3827,7 @@
         <v>0.4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1">
         <v>8.9019999999999992</v>
@@ -3402,7 +3835,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2000</v>
@@ -3411,7 +3844,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1">
         <v>3.6999999999999998E-2</v>
@@ -3420,7 +3853,7 @@
         <v>0.1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1">
         <v>19.32</v>
@@ -3437,70 +3870,114 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.875" customWidth="1"/>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="27.875" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="1">
         <v>2000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>15</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>120</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H2" s="1">
+        <v>195</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.5</v>
       </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3513,55 +3990,99 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="67.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="67.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
+        <v>3120018220</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D2" s="1">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>211</v>
-      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3571,130 +4092,148 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>159</v>
+    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+        <v>275</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="21">
+      <c r="C2" s="21">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3111320634</v>
       </c>
-      <c r="B3" s="21">
+      <c r="C3" s="21">
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3111320635</v>
       </c>
-      <c r="B4" s="21">
+      <c r="C4" s="21">
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3111320636</v>
       </c>
-      <c r="B5" s="21">
+      <c r="C5" s="21">
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+      <c r="B6" s="21">
         <v>3111320637</v>
       </c>
-      <c r="B6" s="21">
+      <c r="C6" s="21">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+      <c r="B7" s="21">
         <v>3110520790</v>
       </c>
-      <c r="B7" s="21">
+      <c r="C7" s="21">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="21">
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+      <c r="B8" s="21">
         <v>1630010773</v>
       </c>
-      <c r="B8" s="21">
+      <c r="C8" s="21">
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+      <c r="B9" s="21">
         <v>2120011658</v>
       </c>
-      <c r="B9" s="21">
+      <c r="C9" s="21">
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+      <c r="B10" s="21">
         <v>3110520789</v>
       </c>
-      <c r="B10" s="22">
+      <c r="C10" s="22">
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+      <c r="B11" s="21">
         <v>2120011659</v>
       </c>
-      <c r="B11" s="22">
+      <c r="C11" s="22">
         <v>0.18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+      <c r="B12" s="21">
         <v>3112230066</v>
       </c>
-      <c r="B12" s="22">
+      <c r="C12" s="22">
         <v>0.22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21">
         <v>2101110225</v>
       </c>
-      <c r="B13" s="22">
+      <c r="C13" s="22">
         <v>0.17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+      <c r="B14" s="21">
         <v>2111410069</v>
       </c>
-      <c r="B14" s="22">
+      <c r="C14" s="22">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="21">
+    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21">
         <v>3112230067</v>
       </c>
-      <c r="B15" s="22">
+      <c r="C15" s="22">
         <v>2E-3</v>
       </c>
     </row>
@@ -3734,82 +4273,82 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="L1" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="S1" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="M1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="T1" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="U1" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="S1" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="T1" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>228</v>
-      </c>
       <c r="V1" s="10" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="W1" s="10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="Y1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="Z1" s="12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
@@ -3817,11 +4356,11 @@
         <v>3120012574</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -3830,7 +4369,7 @@
         <v>2000</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
         <v>2000</v>
@@ -3842,7 +4381,7 @@
         <v>2000</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L2" s="1">
         <v>95</v>
@@ -3885,10 +4424,10 @@
         <v>163.20000000000002</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
@@ -3896,11 +4435,11 @@
         <v>3120012574</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -3909,7 +4448,7 @@
         <v>2001</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H3" s="1">
         <v>2001</v>
@@ -3921,7 +4460,7 @@
         <v>2000</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L3" s="1">
         <v>96</v>
@@ -3964,10 +4503,10 @@
         <v>171</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3988,33 +4527,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" s="1">
         <v>0.13800000000000001</v>
@@ -4023,10 +4562,10 @@
         <v>0.13750000000000001</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1">
         <v>2000</v>
@@ -4034,10 +4573,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1">
         <v>0.127</v>
@@ -4046,10 +4585,10 @@
         <v>0.1268</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G3" s="1">
         <v>2000</v>
@@ -4057,10 +4596,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1">
         <v>21.05</v>
@@ -4069,10 +4608,10 @@
         <v>20.98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G4" s="1">
         <v>2000</v>
@@ -4099,37 +4638,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -4137,11 +4676,11 @@
         <v>3120018220</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -4150,7 +4689,7 @@
         <v>2000</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
         <v>2000</v>
@@ -4162,7 +4701,7 @@
         <v>2000</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -4170,11 +4709,11 @@
         <v>3120018220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -4183,7 +4722,7 @@
         <v>2001</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H3" s="1">
         <v>2001</v>
@@ -4195,7 +4734,7 @@
         <v>2000</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4206,410 +4745,428 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
+        <v>3120018220</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8000142</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="1">
+        <v>8550065300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
+        <v>2120011658</v>
+      </c>
+      <c r="C3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>8000143</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="1">
+        <v>8550065301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
+        <v>3110520789</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>8000144</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8550065302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
+        <v>2120011659</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8000145</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="1">
+        <v>8550065303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+      <c r="B6" s="21">
+        <v>3111320634</v>
+      </c>
+      <c r="C6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>8000146</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="1">
+        <v>8550065304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+      <c r="B7" s="21">
+        <v>3111320635</v>
+      </c>
+      <c r="C7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>8000147</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="1">
+        <v>8550065305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+      <c r="B8" s="21">
+        <v>3111320636</v>
+      </c>
+      <c r="C8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8000148</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="1">
+        <v>8550065306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+      <c r="B9" s="21">
+        <v>3111320637</v>
+      </c>
+      <c r="C9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1">
-        <v>8000142</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I2" s="1">
-        <v>8550065300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
-        <v>2120011658</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="H9" s="1">
+        <v>8000149</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="1">
+        <v>8550065307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+      <c r="B10" s="21">
+        <v>3110520790</v>
+      </c>
+      <c r="C10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>8000150</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="1">
+        <v>8550065308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+      <c r="B11" s="21">
+        <v>1630010773</v>
+      </c>
+      <c r="C11" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8000151</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="1">
+        <v>8550065309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+      <c r="B12" s="21">
+        <v>3112230066</v>
+      </c>
+      <c r="C12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8000152</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8550065310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21">
+        <v>2101110225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8000153</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8550065311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+      <c r="B14" s="21">
+        <v>2111410069</v>
+      </c>
+      <c r="C14" t="s">
         <v>245</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1">
-        <v>8000143</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="1">
-        <v>8550065301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
-        <v>3110520789</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8000154</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="1">
+        <v>8550065312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21">
+        <v>3112230067</v>
+      </c>
+      <c r="C15" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>8000144</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="1">
-        <v>8550065302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
-        <v>2120011659</v>
-      </c>
-      <c r="B5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>8000145</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="1">
-        <v>8550065303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
-        <v>3111320634</v>
-      </c>
-      <c r="B6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8000146</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="1">
-        <v>8550065304</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
-        <v>3111320635</v>
-      </c>
-      <c r="B7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F7" s="1">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>8000147</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="1">
-        <v>8550065305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="21">
-        <v>3111320636</v>
-      </c>
-      <c r="B8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="1">
-        <v>7</v>
-      </c>
-      <c r="G8" s="1">
-        <v>8000148</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="1">
-        <v>8550065306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
-        <v>3111320637</v>
-      </c>
-      <c r="B9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="1">
-        <v>8</v>
-      </c>
-      <c r="G9" s="1">
-        <v>8000149</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="1">
-        <v>8550065307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
-        <v>3110520790</v>
-      </c>
-      <c r="B10" t="s">
-        <v>252</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10" s="1">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1">
-        <v>8000150</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="1">
-        <v>8550065308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
-        <v>1630010773</v>
-      </c>
-      <c r="B11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F11" s="1">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1">
-        <v>8000151</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I11" s="1">
-        <v>8550065309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
-        <v>3112230066</v>
-      </c>
-      <c r="B12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F12" s="1">
-        <v>11</v>
-      </c>
-      <c r="G12" s="1">
-        <v>8000152</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="1">
-        <v>8550065310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
-        <v>2101110225</v>
-      </c>
-      <c r="B13" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F13" s="1">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1">
-        <v>8000153</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="1">
-        <v>8550065311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
-        <v>2111410069</v>
-      </c>
-      <c r="B14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F14" s="1">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1">
-        <v>8000154</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="1">
-        <v>8550065312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="21">
-        <v>3112230067</v>
-      </c>
-      <c r="B15" t="s">
-        <v>257</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>8000155</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="1">
         <v>8550065313</v>
       </c>
     </row>
@@ -4625,109 +5182,111 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" customWidth="1"/>
-    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
+    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
+        <v>3120018220</v>
+      </c>
+      <c r="C2" s="1">
         <v>10</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="1">
-        <v>10</v>
-      </c>
-      <c r="C2" s="21">
+      <c r="D2" s="21">
         <v>2120011658</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="E2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>228</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J2" s="21">
+      <c r="I2" s="1"/>
+      <c r="J2" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="21">
         <v>1</v>
       </c>
-      <c r="K2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="L2" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M2" s="1">
         <v>1</v>
       </c>
-      <c r="M2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0</v>
+      <c r="N2" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -4735,44 +5294,45 @@
       <c r="P2" s="1">
         <v>0</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>20</v>
       </c>
-      <c r="C3" s="21">
+      <c r="D3" s="21">
         <v>2120011659</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="21" t="s">
+        <v>228</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J3" s="21">
+      <c r="I3" s="1"/>
+      <c r="J3" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K3" s="21">
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="L3" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" s="1">
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
+      <c r="N3" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -4780,44 +5340,45 @@
       <c r="P3" s="1">
         <v>0</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>30</v>
       </c>
-      <c r="C4" s="21">
+      <c r="D4" s="21">
         <v>3111320634</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="21" t="s">
+        <v>229</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J4" s="21">
+      <c r="I4" s="1"/>
+      <c r="J4" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K4" s="21">
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="L4" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M4" s="1">
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
+      <c r="N4" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -4825,40 +5386,41 @@
       <c r="P4" s="1">
         <v>0</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>40</v>
       </c>
-      <c r="C5" s="21">
+      <c r="D5" s="21">
         <v>3111320635</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J5" s="21">
+      <c r="E5" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K5" s="21">
         <v>1</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="L5" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
+      <c r="N5" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -4866,40 +5428,41 @@
       <c r="P5" s="1">
         <v>0</v>
       </c>
-      <c r="Q5" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+      <c r="B6" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="C6" s="21">
+      <c r="D6" s="21">
         <v>3111320636</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J6" s="21">
+      <c r="E6" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K6" s="21">
         <v>1</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="L6" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
+      <c r="N6" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -4907,40 +5470,41 @@
       <c r="P6" s="1">
         <v>0</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+      <c r="B7" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <v>60</v>
       </c>
-      <c r="C7" s="21">
+      <c r="D7" s="21">
         <v>3111320637</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J7" s="21">
+      <c r="E7" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K7" s="21">
         <v>1</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="L7" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
+      <c r="N7" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -4948,40 +5512,41 @@
       <c r="P7" s="1">
         <v>0</v>
       </c>
-      <c r="Q7" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="21">
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+      <c r="B8" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <v>70</v>
       </c>
-      <c r="C8" s="21">
+      <c r="D8" s="21">
         <v>3110520790</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J8" s="21">
+      <c r="E8" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K8" s="21">
         <v>2</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="L8" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M8" s="1">
         <v>1</v>
       </c>
-      <c r="M8" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
+      <c r="N8" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -4989,40 +5554,41 @@
       <c r="P8" s="1">
         <v>0</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+      <c r="B9" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C9" s="1">
         <v>80</v>
       </c>
-      <c r="C9" s="21">
+      <c r="D9" s="21">
         <v>1630010773</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J9" s="21">
+      <c r="E9" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="K9" s="21">
         <v>1</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="L9" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M9" s="1">
         <v>1</v>
       </c>
-      <c r="M9" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
+      <c r="N9" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -5030,37 +5596,38 @@
       <c r="P9" s="1">
         <v>0</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+      <c r="B10" s="21">
         <v>2120011658</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="1">
         <v>90</v>
       </c>
-      <c r="C10" s="21">
+      <c r="D10" s="21">
         <v>3110520789</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="J10" s="21">
+      <c r="E10" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="K10" s="21">
         <v>0.36</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="L10" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
+      <c r="N10" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -5068,37 +5635,38 @@
       <c r="P10" s="1">
         <v>0</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+      <c r="B11" s="21">
         <v>2120011658</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C11" s="1">
         <v>100</v>
       </c>
-      <c r="C11" s="21">
+      <c r="D11" s="21">
         <v>3112230066</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="J11" s="21">
+      <c r="E11" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="K11" s="21">
         <v>0.64</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="L11" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M11" s="1">
         <v>1</v>
       </c>
-      <c r="M11" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
+      <c r="N11" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -5106,35 +5674,36 @@
       <c r="P11" s="1">
         <v>0</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+      <c r="B12" s="21">
         <v>3110520789</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C12" s="1">
         <v>110</v>
       </c>
-      <c r="C12" s="21">
+      <c r="D12" s="21">
         <v>2101110225</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="J12" s="21">
+      <c r="E12" s="21"/>
+      <c r="K12" s="21">
         <v>0.3</v>
       </c>
-      <c r="K12" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="L12" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M12" s="1">
         <v>1</v>
       </c>
-      <c r="M12" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
+      <c r="N12" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -5142,34 +5711,35 @@
       <c r="P12" s="1">
         <v>0</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+      <c r="B13" s="21">
         <v>3110520789</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C13" s="1">
         <v>120</v>
       </c>
-      <c r="C13" s="21">
+      <c r="D13" s="21">
         <v>2111410069</v>
       </c>
-      <c r="J13" s="21">
+      <c r="K13" s="21">
         <v>0.7</v>
       </c>
-      <c r="K13" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="L13" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M13" s="1">
         <v>1</v>
       </c>
-      <c r="M13" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
+      <c r="N13" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -5177,34 +5747,35 @@
       <c r="P13" s="1">
         <v>0</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+      <c r="B14" s="21">
         <v>2120011659</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C14" s="1">
         <v>130</v>
       </c>
-      <c r="C14" s="21">
+      <c r="D14" s="21">
         <v>3110520789</v>
       </c>
-      <c r="J14" s="21">
+      <c r="K14" s="21">
         <v>0.30199999999999999</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="L14" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="1">
         <v>1</v>
       </c>
-      <c r="M14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
+      <c r="N14" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -5212,34 +5783,35 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="21">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21">
         <v>2120011659</v>
       </c>
-      <c r="B15" s="1">
+      <c r="C15" s="1">
         <v>140</v>
       </c>
-      <c r="C15" s="21">
+      <c r="D15" s="21">
         <v>3112230067</v>
       </c>
-      <c r="J15" s="21">
+      <c r="K15" s="21">
         <v>0.69799999999999995</v>
       </c>
-      <c r="K15" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="L15" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M15" s="1">
         <v>1</v>
       </c>
-      <c r="M15" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
+      <c r="N15" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -5247,8 +5819,11 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>223</v>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5263,175 +5838,200 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="5" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="6" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="21">
+        <v>2120011658</v>
+      </c>
+      <c r="B2" s="21">
         <v>3112230066</v>
       </c>
-      <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
-      <c r="E2" s="21">
+      <c r="E2" s="21"/>
+      <c r="F2" s="21">
         <v>1</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="G2" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" s="21">
         <v>22</v>
       </c>
-      <c r="H2" s="21">
+      <c r="I2" s="21">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="21">
+        <v>2120011658</v>
+      </c>
+      <c r="B3" s="21">
         <v>3112230066</v>
       </c>
-      <c r="B3" s="21"/>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="21">
+      <c r="E3" s="21"/>
+      <c r="F3" s="21">
         <v>2</v>
       </c>
-      <c r="F3" s="21">
+      <c r="G3" s="21">
         <v>301</v>
       </c>
-      <c r="G3" s="21">
+      <c r="H3" s="21">
         <v>78</v>
       </c>
-      <c r="H3" s="21">
+      <c r="I3" s="21">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="21">
+        <v>3110520789</v>
+      </c>
+      <c r="B4" s="21">
         <v>2101110225</v>
       </c>
-      <c r="B4" s="21"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
-      <c r="E4" s="21">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21">
         <v>1</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="G4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="21">
         <v>90</v>
       </c>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21">
+        <v>3110520789</v>
+      </c>
+      <c r="B5" s="21">
         <v>2101110225</v>
       </c>
-      <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="21">
+      <c r="E5" s="21"/>
+      <c r="F5" s="21">
         <v>2</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="21">
+      <c r="G5" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="21">
         <v>10</v>
       </c>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="21">
+        <v>3110520789</v>
+      </c>
+      <c r="B6" s="21">
         <v>2111410069</v>
       </c>
-      <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="21">
+      <c r="E6" s="21"/>
+      <c r="F6" s="21">
         <v>1</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="G6" s="21">
+      <c r="G6" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" s="21">
         <v>100</v>
       </c>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="21">
+        <v>2120011659</v>
+      </c>
+      <c r="B7" s="21">
         <v>3112230067</v>
       </c>
-      <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="21">
+      <c r="E7" s="21"/>
+      <c r="F7" s="21">
         <v>1</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="G7" s="21">
+      <c r="G7" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="21">
         <v>22</v>
       </c>
-      <c r="H7" s="21"/>
-    </row>
-    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="I7" s="21"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="21">
+        <v>2120011659</v>
+      </c>
+      <c r="B8" s="21">
         <v>3112230067</v>
       </c>
-      <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
-      <c r="E8" s="21">
+      <c r="E8" s="21"/>
+      <c r="F8" s="21">
         <v>2</v>
       </c>
-      <c r="F8" s="21">
+      <c r="G8" s="21">
         <v>301</v>
       </c>
-      <c r="G8" s="21">
+      <c r="H8" s="21">
         <v>78</v>
       </c>
-      <c r="H8" s="21"/>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="I8" s="21"/>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -5439,9 +6039,10 @@
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="I9" s="21"/>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -5449,9 +6050,10 @@
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -5459,9 +6061,10 @@
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
-    </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
@@ -5469,9 +6072,10 @@
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
-    </row>
-    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
@@ -5479,9 +6083,10 @@
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
-    </row>
-    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="I13" s="21"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -5489,9 +6094,10 @@
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="I14" s="21"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -5499,9 +6105,9 @@
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="I15" s="21"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
@@ -5509,9 +6115,9 @@
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
-    </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -5519,9 +6125,9 @@
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
-    </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
@@ -5529,9 +6135,9 @@
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -5539,9 +6145,9 @@
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
-    </row>
-    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="I19" s="21"/>
+    </row>
+    <row r="20" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
@@ -5549,9 +6155,9 @@
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
-    </row>
-    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -5559,9 +6165,9 @@
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
-    </row>
-    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
@@ -5569,9 +6175,9 @@
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-    </row>
-    <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
@@ -5579,9 +6185,9 @@
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
-    </row>
-    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
       <c r="D24" s="21"/>
@@ -5589,9 +6195,9 @@
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
-    </row>
-    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="I24" s="21"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
@@ -5599,9 +6205,9 @@
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
-    </row>
-    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="I25" s="21"/>
+    </row>
+    <row r="26" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
@@ -5609,9 +6215,9 @@
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
-    </row>
-    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="I26" s="21"/>
+    </row>
+    <row r="27" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
@@ -5619,9 +6225,9 @@
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
-    </row>
-    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="I27" s="21"/>
+    </row>
+    <row r="28" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -5629,9 +6235,9 @@
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
-    </row>
-    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -5639,9 +6245,9 @@
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
-    </row>
-    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="I29" s="21"/>
+    </row>
+    <row r="30" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -5649,9 +6255,9 @@
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
-    </row>
-    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="I30" s="21"/>
+    </row>
+    <row r="31" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
@@ -5659,9 +6265,9 @@
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
-    </row>
-    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="I31" s="21"/>
+    </row>
+    <row r="32" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
@@ -5669,9 +6275,9 @@
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
-    </row>
-    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -5679,9 +6285,9 @@
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="H33" s="21"/>
-    </row>
-    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="I33" s="21"/>
+    </row>
+    <row r="34" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -5689,9 +6295,9 @@
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
-    </row>
-    <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
@@ -5699,9 +6305,9 @@
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
       <c r="H35" s="21"/>
-    </row>
-    <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
@@ -5709,9 +6315,9 @@
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
-    </row>
-    <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="I36" s="21"/>
+    </row>
+    <row r="37" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
@@ -5719,9 +6325,9 @@
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
       <c r="H37" s="21"/>
-    </row>
-    <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="I37" s="21"/>
+    </row>
+    <row r="38" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
@@ -5729,9 +6335,9 @@
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
-    </row>
-    <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="I38" s="21"/>
+    </row>
+    <row r="39" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
@@ -5739,9 +6345,9 @@
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
-    </row>
-    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="I39" s="21"/>
+    </row>
+    <row r="40" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
@@ -5749,9 +6355,9 @@
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
-    </row>
-    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="I40" s="21"/>
+    </row>
+    <row r="41" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -5759,9 +6365,9 @@
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-    </row>
-    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="I41" s="21"/>
+    </row>
+    <row r="42" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
@@ -5769,9 +6375,9 @@
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
-    </row>
-    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="I42" s="21"/>
+    </row>
+    <row r="43" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
@@ -5779,9 +6385,9 @@
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
-    </row>
-    <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="I43" s="21"/>
+    </row>
+    <row r="44" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -5789,9 +6395,9 @@
       <c r="F44" s="21"/>
       <c r="G44" s="21"/>
       <c r="H44" s="21"/>
-    </row>
-    <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="I44" s="21"/>
+    </row>
+    <row r="45" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -5799,9 +6405,9 @@
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
       <c r="H45" s="21"/>
-    </row>
-    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="I45" s="21"/>
+    </row>
+    <row r="46" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -5809,9 +6415,9 @@
       <c r="F46" s="21"/>
       <c r="G46" s="21"/>
       <c r="H46" s="21"/>
-    </row>
-    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="I46" s="21"/>
+    </row>
+    <row r="47" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -5819,9 +6425,9 @@
       <c r="F47" s="21"/>
       <c r="G47" s="21"/>
       <c r="H47" s="21"/>
-    </row>
-    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="I47" s="21"/>
+    </row>
+    <row r="48" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -5829,9 +6435,9 @@
       <c r="F48" s="21"/>
       <c r="G48" s="21"/>
       <c r="H48" s="21"/>
-    </row>
-    <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="I48" s="21"/>
+    </row>
+    <row r="49" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
@@ -5839,9 +6445,9 @@
       <c r="F49" s="21"/>
       <c r="G49" s="21"/>
       <c r="H49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="I49" s="21"/>
+    </row>
+    <row r="50" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
@@ -5849,9 +6455,9 @@
       <c r="F50" s="21"/>
       <c r="G50" s="21"/>
       <c r="H50" s="21"/>
-    </row>
-    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="I50" s="21"/>
+    </row>
+    <row r="51" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
@@ -5859,9 +6465,9 @@
       <c r="F51" s="21"/>
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
-    </row>
-    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="I51" s="21"/>
+    </row>
+    <row r="52" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
@@ -5869,9 +6475,9 @@
       <c r="F52" s="21"/>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
-    </row>
-    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
+      <c r="I52" s="21"/>
+    </row>
+    <row r="53" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
@@ -5879,9 +6485,9 @@
       <c r="F53" s="21"/>
       <c r="G53" s="21"/>
       <c r="H53" s="21"/>
-    </row>
-    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
+      <c r="I53" s="21"/>
+    </row>
+    <row r="54" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
@@ -5889,9 +6495,9 @@
       <c r="F54" s="21"/>
       <c r="G54" s="21"/>
       <c r="H54" s="21"/>
-    </row>
-    <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
+      <c r="I54" s="21"/>
+    </row>
+    <row r="55" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
@@ -5899,9 +6505,9 @@
       <c r="F55" s="21"/>
       <c r="G55" s="21"/>
       <c r="H55" s="21"/>
-    </row>
-    <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
+      <c r="I55" s="21"/>
+    </row>
+    <row r="56" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
@@ -5909,9 +6515,9 @@
       <c r="F56" s="21"/>
       <c r="G56" s="21"/>
       <c r="H56" s="21"/>
-    </row>
-    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
+      <c r="I56" s="21"/>
+    </row>
+    <row r="57" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
@@ -5919,9 +6525,9 @@
       <c r="F57" s="21"/>
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
-    </row>
-    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
+      <c r="I57" s="21"/>
+    </row>
+    <row r="58" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
@@ -5929,9 +6535,9 @@
       <c r="F58" s="21"/>
       <c r="G58" s="21"/>
       <c r="H58" s="21"/>
-    </row>
-    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
+      <c r="I58" s="21"/>
+    </row>
+    <row r="59" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
@@ -5939,9 +6545,9 @@
       <c r="F59" s="21"/>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
+      <c r="I59" s="21"/>
+    </row>
+    <row r="60" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
@@ -5949,9 +6555,9 @@
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-    </row>
-    <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
+      <c r="I60" s="21"/>
+    </row>
+    <row r="61" spans="2:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
@@ -5959,6 +6565,7 @@
       <c r="F61" s="21"/>
       <c r="G61" s="21"/>
       <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5972,168 +6579,206 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.5</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="I2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="1">
+        <v>2026060001</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="1">
-        <v>2026060001</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.7</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2026060001</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="1">
-        <v>2026060001</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.4</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="I4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2026060001</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="1">
-        <v>2026060001</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3.0000000000000001E-5</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>2026060001</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="L5" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6147,168 +6792,206 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.625" customWidth="1"/>
-    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21">
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="1">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="1">
         <v>0.02</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J2" s="1">
+        <v>141</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="L2" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2026060002</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2026060002</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="1">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="1">
         <v>0.05</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2026060002</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2026060002</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21">
         <v>3120018220</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="1">
+        <v>111</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1">
         <v>2.5000000000000002E-6</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J5" s="1">
+        <v>145</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="1">
         <v>2026060002</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>145</v>
-      </c>
+      <c r="L5" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
